--- a/Data_HDDT.xlsx
+++ b/Data_HDDT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Works 2\IT\GITHUB\UpSSE_render\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C87EF8-F5E1-4E92-8AC9-78784AF4E205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B3EF3D-C747-4CEB-8E5E-0A2E85B15A7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -840,9 +840,6 @@
     <t>KDNL054</t>
   </si>
   <si>
-    <t>KDNL068</t>
-  </si>
-  <si>
     <t>KDNL060</t>
   </si>
   <si>
@@ -1372,6 +1369,9 @@
   </si>
   <si>
     <t>HH051-010</t>
+  </si>
+  <si>
+    <t>KDNL</t>
   </si>
 </sst>
 </file>
@@ -1890,7 +1890,7 @@
         <v>222</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>182</v>
@@ -1935,10 +1935,10 @@
         <v>10</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>183</v>
@@ -1947,7 +1947,7 @@
         <v>233</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>18</v>
@@ -1976,7 +1976,7 @@
         <v>16</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>192</v>
@@ -1985,7 +1985,7 @@
         <v>17</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>18</v>
@@ -2014,7 +2014,7 @@
         <v>21</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>193</v>
@@ -2023,7 +2023,7 @@
         <v>22</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>18</v>
@@ -2056,7 +2056,7 @@
         <v>28</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>205</v>
@@ -2065,7 +2065,7 @@
         <v>234</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>18</v>
@@ -2094,7 +2094,7 @@
         <v>33</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>217</v>
@@ -2103,7 +2103,7 @@
         <v>235</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>18</v>
@@ -2132,10 +2132,10 @@
         <v>39</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>207</v>
@@ -2144,7 +2144,7 @@
         <v>236</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>18</v>
@@ -2176,7 +2176,7 @@
         <v>43</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>185</v>
@@ -2185,7 +2185,7 @@
         <v>237</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>18</v>
@@ -2217,7 +2217,7 @@
         <v>47</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>197</v>
@@ -2226,7 +2226,7 @@
         <v>226</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>18</v>
@@ -2257,7 +2257,7 @@
         <v>51</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>208</v>
@@ -2266,7 +2266,7 @@
         <v>52</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>18</v>
@@ -2297,7 +2297,7 @@
         <v>56</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>194</v>
@@ -2306,7 +2306,7 @@
         <v>238</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>18</v>
@@ -2318,7 +2318,7 @@
     </row>
     <row r="14" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B14" s="1">
         <v>0</v>
@@ -2339,7 +2339,7 @@
         <v>61</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>202</v>
@@ -2348,7 +2348,7 @@
         <v>62</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>18</v>
@@ -2375,7 +2375,7 @@
         <v>67</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>196</v>
@@ -2384,7 +2384,7 @@
         <v>239</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>18</v>
@@ -2408,7 +2408,7 @@
         <v>71</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>209</v>
@@ -2417,7 +2417,7 @@
         <v>240</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>18</v>
@@ -2443,7 +2443,7 @@
         <v>76</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>200</v>
@@ -2452,7 +2452,7 @@
         <v>241</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>18</v>
@@ -2475,10 +2475,10 @@
         <v>80</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>189</v>
@@ -2487,13 +2487,13 @@
         <v>227</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>227</v>
+        <v>444</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
@@ -2513,7 +2513,7 @@
         <v>85</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>187</v>
@@ -2522,7 +2522,7 @@
         <v>228</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>18</v>
@@ -2548,7 +2548,7 @@
         <v>90</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>210</v>
@@ -2557,7 +2557,7 @@
         <v>91</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>18</v>
@@ -2580,10 +2580,10 @@
         <v>95</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>191</v>
@@ -2592,7 +2592,7 @@
         <v>96</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>18</v>
@@ -2606,7 +2606,7 @@
         <v>97</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>98</v>
@@ -2621,10 +2621,10 @@
         <v>101</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>188</v>
@@ -2633,7 +2633,7 @@
         <v>229</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>18</v>
@@ -2659,7 +2659,7 @@
         <v>106</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>190</v>
@@ -2668,7 +2668,7 @@
         <v>107</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>18</v>
@@ -2691,10 +2691,10 @@
         <v>111</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>199</v>
@@ -2703,7 +2703,7 @@
         <v>112</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>18</v>
@@ -2726,10 +2726,10 @@
         <v>116</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>198</v>
@@ -2738,7 +2738,7 @@
         <v>230</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>18</v>
@@ -2768,7 +2768,7 @@
         <v>232</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>213</v>
@@ -2777,7 +2777,7 @@
         <v>242</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>18</v>
@@ -2803,7 +2803,7 @@
         <v>125</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>211</v>
@@ -2812,7 +2812,7 @@
         <v>243</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>18</v>
@@ -2839,7 +2839,7 @@
         <v>130</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>212</v>
@@ -2848,7 +2848,7 @@
         <v>244</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>18</v>
@@ -2880,7 +2880,7 @@
         <v>135</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>214</v>
@@ -2889,7 +2889,7 @@
         <v>245</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>18</v>
@@ -2918,10 +2918,10 @@
         <v>139</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>204</v>
@@ -2930,13 +2930,13 @@
         <v>246</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>267</v>
+        <v>444</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -2962,7 +2962,7 @@
         <v>144</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>186</v>
@@ -2971,7 +2971,7 @@
         <v>145</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>18</v>
@@ -3001,7 +3001,7 @@
         <v>150</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>215</v>
@@ -3010,13 +3010,13 @@
         <v>247</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3039,7 +3039,7 @@
         <v>154</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>206</v>
@@ -3048,13 +3048,13 @@
         <v>248</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3077,7 +3077,7 @@
         <v>158</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>216</v>
@@ -3086,13 +3086,13 @@
         <v>249</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3115,7 +3115,7 @@
         <v>162</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>195</v>
@@ -3124,13 +3124,13 @@
         <v>163</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3153,7 +3153,7 @@
         <v>167</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>203</v>
@@ -3162,13 +3162,13 @@
         <v>250</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3189,10 +3189,10 @@
         <v>172</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>184</v>
@@ -3201,13 +3201,13 @@
         <v>251</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3230,10 +3230,10 @@
         <v>176</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>218</v>
@@ -3242,13 +3242,13 @@
         <v>252</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3271,10 +3271,10 @@
         <v>180</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>201</v>
@@ -3283,7 +3283,7 @@
         <v>231</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>18</v>
@@ -3300,69 +3300,69 @@
         <v>333115</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="H40" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="I40" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="J40" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>291</v>
-      </c>
       <c r="K40" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N40" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="M40" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="D41" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="K41" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="K41" s="1" t="s">
+      <c r="L41" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N41" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="M41" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3371,34 +3371,34 @@
       </c>
       <c r="B42" s="10"/>
       <c r="D42" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="K42" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="K42" s="1" t="s">
+      <c r="L42" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N42" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3407,34 +3407,34 @@
       </c>
       <c r="B43" s="10"/>
       <c r="D43" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="L43" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="M43" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3445,34 +3445,34 @@
         <v>131111</v>
       </c>
       <c r="D44" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="G44" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="H44" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="I44" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="K44" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="I44" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="K44" s="1" t="s">
+      <c r="L44" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N44" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3483,34 +3483,34 @@
         <v>131112</v>
       </c>
       <c r="D45" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="K45" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="F45" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="K45" s="1" t="s">
+      <c r="L45" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="L45" s="1" t="s">
+      <c r="M45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N45" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N45" s="1" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3521,34 +3521,34 @@
         <v>131114</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N46" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="M46" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N46" s="1" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3557,28 +3557,28 @@
       </c>
       <c r="B47" s="10"/>
       <c r="D47" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="K47" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="K47" s="1" t="s">
+      <c r="L47" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N47" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="L47" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="M47" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N47" s="1" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3589,31 +3589,31 @@
         <v>3338111</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G48" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="H48" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="I48" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="I48" s="1" t="s">
+      <c r="J48" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>439</v>
-      </c>
       <c r="K48" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3624,31 +3624,31 @@
         <v>3338121</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G49" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="I49" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="I49" s="1" t="s">
+      <c r="J49" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="K49" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">

--- a/Data_HDDT.xlsx
+++ b/Data_HDDT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Works 2\IT\GITHUB\UpSSE_render\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B3EF3D-C747-4CEB-8E5E-0A2E85B15A7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F435960B-7E00-4453-8515-A3F5D495F5BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1371,7 +1371,7 @@
     <t>HH051-010</t>
   </si>
   <si>
-    <t>KDNL</t>
+    <t>KDNL068</t>
   </si>
 </sst>
 </file>
@@ -2493,7 +2493,7 @@
         <v>18</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>444</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">

--- a/Data_HDDT.xlsx
+++ b/Data_HDDT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Works 2\IT\GITHUB\UpSSE_render\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F435960B-7E00-4453-8515-A3F5D495F5BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9588CC02-D147-4897-A7EE-192F9135ECC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="459">
   <si>
     <t>Mã kho</t>
   </si>
@@ -1372,6 +1372,48 @@
   </si>
   <si>
     <t>KDNL068</t>
+  </si>
+  <si>
+    <t>Bảo Minh</t>
+  </si>
+  <si>
+    <t>Đại Thắng</t>
+  </si>
+  <si>
+    <t>HH051-052</t>
+  </si>
+  <si>
+    <t>HH009-012</t>
+  </si>
+  <si>
+    <t>HH050-048</t>
+  </si>
+  <si>
+    <t>HH0647</t>
+  </si>
+  <si>
+    <t>KDNL087</t>
+  </si>
+  <si>
+    <t>KDNL187</t>
+  </si>
+  <si>
+    <t>1K26TBM</t>
+  </si>
+  <si>
+    <t>1K26TĐT</t>
+  </si>
+  <si>
+    <t>KDNL088</t>
+  </si>
+  <si>
+    <t>KDNL188</t>
+  </si>
+  <si>
+    <t>HH051-053</t>
+  </si>
+  <si>
+    <t>HH009-013</t>
   </si>
 </sst>
 </file>
@@ -1860,7 +1902,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:Q55"/>
+  <dimension ref="A1:Q55"/>
   <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -1876,6 +1918,7 @@
     <col min="392" max="16384" width="8.42578125" style="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:17" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E2" s="1" t="s">
         <v>224</v>
@@ -3658,6 +3701,33 @@
       <c r="B50" s="10">
         <v>333814</v>
       </c>
+      <c r="D50" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="51" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="11" t="s">
@@ -3665,6 +3735,27 @@
       </c>
       <c r="B51" s="10">
         <v>63211</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">

--- a/Data_HDDT.xlsx
+++ b/Data_HDDT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Works 2\IT\GITHUB\UpSSE_render\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9588CC02-D147-4897-A7EE-192F9135ECC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC37738-DDAC-42DB-8EB0-F58D78763691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhap lieu" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="466">
   <si>
     <t>Mã kho</t>
   </si>
@@ -1414,6 +1414,27 @@
   </si>
   <si>
     <t>HH009-013</t>
+  </si>
+  <si>
+    <t>HH009-015</t>
+  </si>
+  <si>
+    <t>HH050-051</t>
+  </si>
+  <si>
+    <t>HH051-055</t>
+  </si>
+  <si>
+    <t>KDNL190</t>
+  </si>
+  <si>
+    <t>KDNL090</t>
+  </si>
+  <si>
+    <t>Lạc Quần</t>
+  </si>
+  <si>
+    <t>1K26TLQ</t>
   </si>
 </sst>
 </file>
@@ -1903,23 +1924,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:Q55"/>
-  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="9.9" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" style="1" customWidth="1"/>
-    <col min="11" max="391" width="8.42578125" style="1" customWidth="1"/>
-    <col min="392" max="16384" width="8.42578125" style="1"/>
+    <col min="10" max="10" width="11.44140625" style="1" customWidth="1"/>
+    <col min="11" max="391" width="8.44140625" style="1" customWidth="1"/>
+    <col min="392" max="16384" width="8.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="9.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E2" s="1" t="s">
         <v>224</v>
       </c>
@@ -1951,14 +1972,14 @@
         <v>253</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
     </row>
-    <row r="4" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>224</v>
       </c>
@@ -1999,7 +2020,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>225</v>
       </c>
@@ -2037,7 +2058,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>223</v>
       </c>
@@ -2075,7 +2096,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" s="6" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>222</v>
       </c>
@@ -2119,7 +2140,7 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:17" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" s="6" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="1"/>
       <c r="D8" s="4" t="s">
         <v>29</v>
@@ -2157,7 +2178,7 @@
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:17" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" s="6" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>35</v>
       </c>
@@ -2198,7 +2219,7 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:17" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" s="6" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>223</v>
       </c>
@@ -2239,7 +2260,7 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:17" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>224</v>
       </c>
@@ -2279,7 +2300,7 @@
       </c>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:17" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>225</v>
       </c>
@@ -2319,7 +2340,7 @@
       </c>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:17" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" s="6" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>222</v>
       </c>
@@ -2359,7 +2380,7 @@
       </c>
       <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>374</v>
       </c>
@@ -2401,7 +2422,7 @@
       </c>
       <c r="P14" s="6"/>
     </row>
-    <row r="15" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D15" s="4" t="s">
         <v>63</v>
       </c>
@@ -2436,7 +2457,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="D16" s="4" t="s">
         <v>68</v>
@@ -2469,7 +2490,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D17" s="4" t="s">
         <v>72</v>
       </c>
@@ -2504,7 +2525,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D18" s="4" t="s">
         <v>77</v>
       </c>
@@ -2539,7 +2560,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D19" s="4" t="s">
         <v>81</v>
       </c>
@@ -2574,7 +2595,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D20" s="4" t="s">
         <v>86</v>
       </c>
@@ -2609,7 +2630,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D21" s="4" t="s">
         <v>92</v>
       </c>
@@ -2644,7 +2665,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>97</v>
       </c>
@@ -2685,7 +2706,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D23" s="4" t="s">
         <v>102</v>
       </c>
@@ -2720,7 +2741,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D24" s="4" t="s">
         <v>108</v>
       </c>
@@ -2755,7 +2776,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D25" s="4" t="s">
         <v>113</v>
       </c>
@@ -2790,7 +2811,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>117</v>
       </c>
@@ -2830,7 +2851,7 @@
       </c>
       <c r="P26" s="2"/>
     </row>
-    <row r="27" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="D27" s="4" t="s">
@@ -2864,7 +2885,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>126</v>
       </c>
@@ -2900,7 +2921,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>18</v>
       </c>
@@ -2941,7 +2962,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>34</v>
       </c>
@@ -2982,7 +3003,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>11</v>
       </c>
@@ -3023,7 +3044,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>219</v>
       </c>
@@ -3062,7 +3083,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>18</v>
       </c>
@@ -3100,7 +3121,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>34</v>
       </c>
@@ -3138,7 +3159,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>11</v>
       </c>
@@ -3176,7 +3197,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>220</v>
       </c>
@@ -3214,7 +3235,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>168</v>
       </c>
@@ -3253,7 +3274,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>18</v>
       </c>
@@ -3294,7 +3315,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>34</v>
       </c>
@@ -3335,7 +3356,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
         <v>11</v>
       </c>
@@ -3374,7 +3395,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="D41" s="1" t="s">
@@ -3408,7 +3429,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
         <v>181</v>
       </c>
@@ -3444,7 +3465,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>126</v>
       </c>
@@ -3480,7 +3501,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>18</v>
       </c>
@@ -3518,7 +3539,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>34</v>
       </c>
@@ -3556,7 +3577,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
         <v>11</v>
       </c>
@@ -3594,7 +3615,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
         <v>221</v>
       </c>
@@ -3624,7 +3645,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>18</v>
       </c>
@@ -3659,7 +3680,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>34</v>
       </c>
@@ -3694,7 +3715,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>11</v>
       </c>
@@ -3729,7 +3750,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
         <v>220</v>
       </c>
@@ -3758,13 +3779,37 @@
         <v>455</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
         <v>168</v>
       </c>
       <c r="B52" s="10"/>
-    </row>
-    <row r="53" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D52" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>18</v>
       </c>
@@ -3772,7 +3817,7 @@
         <v>333111</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
         <v>34</v>
       </c>
@@ -3780,7 +3825,7 @@
         <v>333112</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>11</v>
       </c>

--- a/Data_HDDT.xlsx
+++ b/Data_HDDT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Works 2\IT\GITHUB\UpSSE_render\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC37738-DDAC-42DB-8EB0-F58D78763691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E564A9-170C-4F10-982B-0CA66CA99FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhap lieu" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="473">
   <si>
     <t>Mã kho</t>
   </si>
@@ -1435,6 +1435,27 @@
   </si>
   <si>
     <t>1K26TLQ</t>
+  </si>
+  <si>
+    <t>Khánh Thiện</t>
+  </si>
+  <si>
+    <t>HH051-054</t>
+  </si>
+  <si>
+    <t>HH050-050</t>
+  </si>
+  <si>
+    <t>HH009-014</t>
+  </si>
+  <si>
+    <t>KDNL189</t>
+  </si>
+  <si>
+    <t>KDNL089</t>
+  </si>
+  <si>
+    <t>1K26TAH</t>
   </si>
 </sst>
 </file>
@@ -1555,7 +1576,18 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1924,23 +1956,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:Q55"/>
-  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="9.9" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.44140625" style="1" customWidth="1"/>
-    <col min="11" max="391" width="8.44140625" style="1" customWidth="1"/>
-    <col min="392" max="16384" width="8.44140625" style="1"/>
+    <col min="10" max="10" width="11.42578125" style="1" customWidth="1"/>
+    <col min="11" max="391" width="8.42578125" style="1" customWidth="1"/>
+    <col min="392" max="16384" width="8.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="9.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E2" s="1" t="s">
         <v>224</v>
       </c>
@@ -1972,14 +2004,14 @@
         <v>253</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
     </row>
-    <row r="4" spans="1:17" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>224</v>
       </c>
@@ -2020,7 +2052,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>225</v>
       </c>
@@ -2058,7 +2090,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>223</v>
       </c>
@@ -2096,7 +2128,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="6" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>222</v>
       </c>
@@ -2140,7 +2172,7 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:17" s="6" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="1"/>
       <c r="D8" s="4" t="s">
         <v>29</v>
@@ -2178,7 +2210,7 @@
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:17" s="6" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>35</v>
       </c>
@@ -2219,7 +2251,7 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:17" s="6" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>223</v>
       </c>
@@ -2260,7 +2292,7 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:17" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>224</v>
       </c>
@@ -2300,7 +2332,7 @@
       </c>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:17" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>225</v>
       </c>
@@ -2340,7 +2372,7 @@
       </c>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:17" s="6" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>222</v>
       </c>
@@ -2380,7 +2412,7 @@
       </c>
       <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="1:17" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>374</v>
       </c>
@@ -2422,7 +2454,7 @@
       </c>
       <c r="P14" s="6"/>
     </row>
-    <row r="15" spans="1:17" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="4" t="s">
         <v>63</v>
       </c>
@@ -2457,7 +2489,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="D16" s="4" t="s">
         <v>68</v>
@@ -2490,7 +2522,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D17" s="4" t="s">
         <v>72</v>
       </c>
@@ -2525,7 +2557,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="4" t="s">
         <v>77</v>
       </c>
@@ -2560,7 +2592,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="4" t="s">
         <v>81</v>
       </c>
@@ -2595,7 +2627,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="4" t="s">
         <v>86</v>
       </c>
@@ -2630,7 +2662,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="4" t="s">
         <v>92</v>
       </c>
@@ -2665,7 +2697,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>97</v>
       </c>
@@ -2706,7 +2738,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="4" t="s">
         <v>102</v>
       </c>
@@ -2741,7 +2773,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="4" t="s">
         <v>108</v>
       </c>
@@ -2776,7 +2808,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="4" t="s">
         <v>113</v>
       </c>
@@ -2811,7 +2843,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
         <v>117</v>
       </c>
@@ -2851,7 +2883,7 @@
       </c>
       <c r="P26" s="2"/>
     </row>
-    <row r="27" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="D27" s="4" t="s">
@@ -2885,7 +2917,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
         <v>126</v>
       </c>
@@ -2921,7 +2953,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
         <v>18</v>
       </c>
@@ -2962,7 +2994,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
         <v>34</v>
       </c>
@@ -3003,7 +3035,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="s">
         <v>11</v>
       </c>
@@ -3044,7 +3076,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="11" t="s">
         <v>219</v>
       </c>
@@ -3083,7 +3115,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="10" t="s">
         <v>18</v>
       </c>
@@ -3121,7 +3153,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="10" t="s">
         <v>34</v>
       </c>
@@ -3159,7 +3191,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
         <v>11</v>
       </c>
@@ -3197,7 +3229,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
         <v>220</v>
       </c>
@@ -3235,7 +3267,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
         <v>168</v>
       </c>
@@ -3274,7 +3306,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="10" t="s">
         <v>18</v>
       </c>
@@ -3315,7 +3347,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="10" t="s">
         <v>34</v>
       </c>
@@ -3356,7 +3388,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="10" t="s">
         <v>11</v>
       </c>
@@ -3395,7 +3427,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="D41" s="1" t="s">
@@ -3429,7 +3461,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
         <v>181</v>
       </c>
@@ -3465,7 +3497,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="11" t="s">
         <v>126</v>
       </c>
@@ -3501,7 +3533,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="10" t="s">
         <v>18</v>
       </c>
@@ -3539,7 +3571,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="10" t="s">
         <v>34</v>
       </c>
@@ -3577,7 +3609,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="10" t="s">
         <v>11</v>
       </c>
@@ -3615,7 +3647,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="11" t="s">
         <v>221</v>
       </c>
@@ -3645,7 +3677,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="10" t="s">
         <v>18</v>
       </c>
@@ -3680,7 +3712,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="10" t="s">
         <v>34</v>
       </c>
@@ -3715,7 +3747,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="10" t="s">
         <v>11</v>
       </c>
@@ -3750,7 +3782,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="11" t="s">
         <v>220</v>
       </c>
@@ -3779,7 +3811,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="11" t="s">
         <v>168</v>
       </c>
@@ -3809,15 +3841,39 @@
         <v>463</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B53" s="10">
         <v>333111</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D53" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="10" t="s">
         <v>34</v>
       </c>
@@ -3825,7 +3881,7 @@
         <v>333112</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="10" t="s">
         <v>11</v>
       </c>
@@ -3834,6 +3890,9 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="L1:L1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0"/>
 </worksheet>

--- a/Data_HDDT.xlsx
+++ b/Data_HDDT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Works 2\IT\GITHUB\UpSSE_render\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E564A9-170C-4F10-982B-0CA66CA99FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C515E32-6D17-4A47-BDE0-F2EBBE0B0F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="474">
   <si>
     <t>Mã kho</t>
   </si>
@@ -1456,6 +1456,9 @@
   </si>
   <si>
     <t>1K26TAH</t>
+  </si>
+  <si>
+    <t>Xăng E10 RON 95 Mức 3</t>
   </si>
 </sst>
 </file>
@@ -2414,7 +2417,7 @@
     </row>
     <row r="14" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>374</v>
+        <v>473</v>
       </c>
       <c r="B14" s="1">
         <v>0</v>

--- a/Data_HDDT.xlsx
+++ b/Data_HDDT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Works 2\IT\GITHUB\UpSSE_render\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C515E32-6D17-4A47-BDE0-F2EBBE0B0F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E553F52B-D0F3-46C6-8C62-EC5E94CB85CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="473">
   <si>
     <t>Mã kho</t>
   </si>
@@ -1159,9 +1159,6 @@
   </si>
   <si>
     <t>HH0643</t>
-  </si>
-  <si>
-    <t>Xăng E10 RON95 Mức 3</t>
   </si>
   <si>
     <t>HH051-034</t>
@@ -1989,7 +1986,7 @@
         <v>222</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>374</v>
+        <v>472</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>182</v>
@@ -2037,7 +2034,7 @@
         <v>282</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>183</v>
@@ -2075,7 +2072,7 @@
         <v>16</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>192</v>
@@ -2113,7 +2110,7 @@
         <v>21</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>193</v>
@@ -2155,7 +2152,7 @@
         <v>28</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>205</v>
@@ -2193,7 +2190,7 @@
         <v>33</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>217</v>
@@ -2234,7 +2231,7 @@
         <v>281</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>207</v>
@@ -2275,7 +2272,7 @@
         <v>43</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>185</v>
@@ -2316,7 +2313,7 @@
         <v>47</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>197</v>
@@ -2356,7 +2353,7 @@
         <v>51</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>208</v>
@@ -2396,7 +2393,7 @@
         <v>56</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>194</v>
@@ -2417,7 +2414,7 @@
     </row>
     <row r="14" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B14" s="1">
         <v>0</v>
@@ -2438,7 +2435,7 @@
         <v>61</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>202</v>
@@ -2474,7 +2471,7 @@
         <v>67</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>196</v>
@@ -2507,7 +2504,7 @@
         <v>71</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>209</v>
@@ -2542,7 +2539,7 @@
         <v>76</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>200</v>
@@ -2577,7 +2574,7 @@
         <v>275</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>189</v>
@@ -2612,7 +2609,7 @@
         <v>85</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>187</v>
@@ -2647,7 +2644,7 @@
         <v>90</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>210</v>
@@ -2682,7 +2679,7 @@
         <v>278</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>191</v>
@@ -2723,7 +2720,7 @@
         <v>276</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>188</v>
@@ -2758,7 +2755,7 @@
         <v>106</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>190</v>
@@ -2793,7 +2790,7 @@
         <v>279</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>199</v>
@@ -2828,7 +2825,7 @@
         <v>274</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>198</v>
@@ -2867,7 +2864,7 @@
         <v>232</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>213</v>
@@ -2902,7 +2899,7 @@
         <v>125</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>211</v>
@@ -2938,7 +2935,7 @@
         <v>130</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>212</v>
@@ -2979,7 +2976,7 @@
         <v>135</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>214</v>
@@ -3020,7 +3017,7 @@
         <v>346</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>204</v>
@@ -3035,7 +3032,7 @@
         <v>18</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3061,7 +3058,7 @@
         <v>144</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>186</v>
@@ -3100,7 +3097,7 @@
         <v>150</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>215</v>
@@ -3138,7 +3135,7 @@
         <v>154</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>206</v>
@@ -3176,7 +3173,7 @@
         <v>158</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>216</v>
@@ -3214,7 +3211,7 @@
         <v>162</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>195</v>
@@ -3252,7 +3249,7 @@
         <v>167</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>203</v>
@@ -3291,7 +3288,7 @@
         <v>277</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>184</v>
@@ -3332,7 +3329,7 @@
         <v>283</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>218</v>
@@ -3373,7 +3370,7 @@
         <v>280</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>201</v>
@@ -3412,7 +3409,7 @@
         <v>289</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>290</v>
@@ -3446,7 +3443,7 @@
         <v>296</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>297</v>
@@ -3482,7 +3479,7 @@
         <v>303</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>304</v>
@@ -3518,7 +3515,7 @@
         <v>348</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>351</v>
@@ -3556,10 +3553,10 @@
         <v>355</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>356</v>
@@ -3594,10 +3591,10 @@
         <v>365</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="K45" s="1" t="s">
         <v>360</v>
@@ -3632,13 +3629,13 @@
         <v>372</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>373</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>368</v>
@@ -3656,28 +3653,28 @@
       </c>
       <c r="B47" s="10"/>
       <c r="D47" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="K47" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="K47" s="1" t="s">
+      <c r="L47" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N47" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="L47" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="M47" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N47" s="1" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3688,31 +3685,31 @@
         <v>3338111</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G48" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="H48" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="I48" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="I48" s="1" t="s">
+      <c r="J48" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="K48" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3723,31 +3720,31 @@
         <v>3338121</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G49" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="I49" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="I49" s="1" t="s">
+      <c r="J49" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="K49" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3758,31 +3755,31 @@
         <v>333814</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G50" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="H50" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="I50" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="J50" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="I50" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="J50" s="1" t="s">
+      <c r="K50" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N50" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="L50" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="M50" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N50" s="1" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3793,25 +3790,25 @@
         <v>63211</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L51" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N51" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="M51" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N51" s="1" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3820,28 +3817,28 @@
       </c>
       <c r="B52" s="10"/>
       <c r="D52" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="L52" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="K52" s="1" t="s">
+      <c r="M52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N52" s="1" t="s">
         <v>462</v>
-      </c>
-      <c r="L52" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="M52" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N52" s="1" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3852,28 +3849,28 @@
         <v>333111</v>
       </c>
       <c r="D53" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="I53" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="K53" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="H53" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="K53" s="1" t="s">
+      <c r="L53" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N53" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="M53" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">

--- a/Data_HDDT.xlsx
+++ b/Data_HDDT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Works 2\IT\GITHUB\UpSSE_render\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E553F52B-D0F3-46C6-8C62-EC5E94CB85CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E639BAA-64A4-47EF-8EBD-AF0939D1E609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1398,9 +1398,6 @@
     <t>1K26TBM</t>
   </si>
   <si>
-    <t>1K26TĐT</t>
-  </si>
-  <si>
     <t>KDNL088</t>
   </si>
   <si>
@@ -1456,6 +1453,9 @@
   </si>
   <si>
     <t>Xăng E10 RON 95 Mức 3</t>
+  </si>
+  <si>
+    <t>1K26TDT</t>
   </si>
 </sst>
 </file>
@@ -1986,7 +1986,7 @@
         <v>222</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>182</v>
@@ -2414,7 +2414,7 @@
     </row>
     <row r="14" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B14" s="1">
         <v>0</v>
@@ -3793,22 +3793,22 @@
         <v>445</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L51" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N51" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="M51" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N51" s="1" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3817,28 +3817,28 @@
       </c>
       <c r="B52" s="10"/>
       <c r="D52" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="L52" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="K52" s="1" t="s">
+      <c r="M52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N52" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="L52" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="M52" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N52" s="1" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3849,28 +3849,28 @@
         <v>333111</v>
       </c>
       <c r="D53" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="I53" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="K53" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="H53" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="K53" s="1" t="s">
+      <c r="L53" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N53" s="1" t="s">
         <v>469</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="M53" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">

--- a/Data_HDDT.xlsx
+++ b/Data_HDDT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Works 2\IT\GITHUB\UpSSE_render\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E639BAA-64A4-47EF-8EBD-AF0939D1E609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{317AF646-3721-44B7-B966-6F38E1A0E36D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="481">
   <si>
     <t>Mã kho</t>
   </si>
@@ -1456,6 +1456,30 @@
   </si>
   <si>
     <t>1K26TDT</t>
+  </si>
+  <si>
+    <t>Ý Yên</t>
+  </si>
+  <si>
+    <t>HH051-056</t>
+  </si>
+  <si>
+    <t>HH050-052</t>
+  </si>
+  <si>
+    <t>HH009-016</t>
+  </si>
+  <si>
+    <t>HH0651</t>
+  </si>
+  <si>
+    <t>1K26TYY</t>
+  </si>
+  <si>
+    <t>KDNL192</t>
+  </si>
+  <si>
+    <t>KDNL092</t>
   </si>
 </sst>
 </file>
@@ -3880,6 +3904,33 @@
       <c r="B54" s="10">
         <v>333112</v>
       </c>
+      <c r="D54" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>480</v>
+      </c>
     </row>
     <row r="55" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="10" t="s">
